--- a/data/2026/cjsl/fall/brooklyn-city-fc-b15-16-blue.xlsx
+++ b/data/2026/cjsl/fall/brooklyn-city-fc-b15-16-blue.xlsx
@@ -78,7 +78,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" width="46.2"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="59.400000000000006"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="18.700000000000003"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="5.5"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -214,7 +214,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/brooklyn-city-fc-b15-16-blue.xlsx
+++ b/data/2026/cjsl/fall/brooklyn-city-fc-b15-16-blue.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 - 2</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/brooklyn-city-fc-b15-16-blue.xlsx
+++ b/data/2026/cjsl/fall/brooklyn-city-fc-b15-16-blue.xlsx
@@ -284,7 +284,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 - 4</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/brooklyn-city-fc-b15-16-blue.xlsx
+++ b/data/2026/cjsl/fall/brooklyn-city-fc-b15-16-blue.xlsx
@@ -329,7 +329,7 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0 - 5</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
